--- a/analysis/recap/at-PRF.xlsx
+++ b/analysis/recap/at-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -503,13 +503,13 @@
         <v>14298463</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.8343558282208589</v>
       </c>
       <c r="I2" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7813411078717202</v>
+        <v>0.8168168168168169</v>
       </c>
     </row>
     <row r="3">
@@ -520,7 +520,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -547,13 +547,13 @@
         <v>30288239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8433734939759037</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7941176470588235</v>
       </c>
     </row>
     <row r="4">
@@ -564,7 +564,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,13 +591,13 @@
         <v>42511865</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="I4" t="n">
-        <v>0.788235294117647</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7813411078717202</v>
+        <v>0.7764705882352941</v>
       </c>
     </row>
     <row r="5">
@@ -608,7 +608,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -635,13 +635,13 @@
         <v>50995999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7904191616766467</v>
+        <v>0.8192771084337349</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.8</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7833827893175075</v>
+        <v>0.8095238095238095</v>
       </c>
     </row>
     <row r="6">
@@ -652,7 +652,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -679,13 +679,13 @@
         <v>246773155</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7951807228915663</v>
+        <v>0.791907514450867</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.8058823529411765</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7988338192419824</v>
       </c>
     </row>
     <row r="7">
@@ -696,7 +696,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -706,30 +706,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>14298463</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.8414634146341463</v>
       </c>
       <c r="I7" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8117647058823529</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7813411078717202</v>
+        <v>0.8263473053892215</v>
       </c>
     </row>
     <row r="8">
@@ -740,7 +740,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -750,30 +750,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>30288239</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8433734939759037</v>
+        <v>0.7797619047619048</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.7705882352941177</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7751479289940829</v>
       </c>
     </row>
     <row r="9">
@@ -784,7 +784,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -794,30 +794,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>42511865</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="I9" t="n">
-        <v>0.788235294117647</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7813411078717202</v>
+        <v>0.7764705882352941</v>
       </c>
     </row>
     <row r="10">
@@ -828,7 +828,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -838,30 +838,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>50995999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7904191616766467</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.7823529411764706</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7833827893175075</v>
+        <v>0.7869822485207101</v>
       </c>
     </row>
     <row r="11">
@@ -872,7 +872,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -882,30 +882,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>246773155</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7951807228915663</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.8117647058823529</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.8023255813953488</v>
       </c>
     </row>
     <row r="12">
@@ -916,7 +916,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -943,13 +943,13 @@
         <v>14298463</v>
       </c>
       <c r="H12" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8121212121212121</v>
       </c>
       <c r="I12" t="n">
         <v>0.788235294117647</v>
       </c>
       <c r="J12" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13">
@@ -960,7 +960,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -987,13 +987,13 @@
         <v>30288239</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7987804878048781</v>
+        <v>0.7456647398843931</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7705882352941177</v>
+        <v>0.7588235294117647</v>
       </c>
       <c r="J13" t="n">
-        <v>0.784431137724551</v>
+        <v>0.7521865889212828</v>
       </c>
     </row>
     <row r="14">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1031,13 +1031,13 @@
         <v>42511865</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7797619047619048</v>
+        <v>0.7674418604651163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7705882352941177</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7751479289940829</v>
+        <v>0.7719298245614037</v>
       </c>
     </row>
     <row r="15">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1075,13 +1075,13 @@
         <v>50995999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7848837209302325</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="I15" t="n">
         <v>0.7941176470588235</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7894736842105262</v>
+        <v>0.8059701492537314</v>
       </c>
     </row>
     <row r="16">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1119,13 +1119,13 @@
         <v>246773155</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8023255813953488</v>
+        <v>0.8143712574850299</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8117647058823529</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8070175438596492</v>
+        <v>0.8071216617210683</v>
       </c>
     </row>
     <row r="17">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1156,20 +1156,20 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>14298463</v>
       </c>
       <c r="H17" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8</v>
       </c>
       <c r="I17" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8000000000000002</v>
       </c>
     </row>
     <row r="18">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1200,20 +1200,20 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>30288239</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7987804878048781</v>
+        <v>0.7456647398843931</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7705882352941177</v>
+        <v>0.7588235294117647</v>
       </c>
       <c r="J18" t="n">
-        <v>0.784431137724551</v>
+        <v>0.7521865889212828</v>
       </c>
     </row>
     <row r="19">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1244,20 +1244,20 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>42511865</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7797619047619048</v>
+        <v>0.7810650887573964</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7705882352941177</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7751479289940829</v>
+        <v>0.7787610619469028</v>
       </c>
     </row>
     <row r="20">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1288,20 +1288,20 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>50995999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7848837209302325</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.7823529411764706</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7894736842105262</v>
+        <v>0.7869822485207101</v>
       </c>
     </row>
     <row r="21">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1332,20 +1332,20 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>246773155</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8023255813953488</v>
+        <v>0.7869822485207101</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8117647058823529</v>
+        <v>0.7823529411764706</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8070175438596492</v>
+        <v>0.7846607669616519</v>
       </c>
     </row>
     <row r="22">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1380,16 +1380,16 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8103448275862069</v>
+        <v>0.8058823529411765</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.7828571428571428</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8080229226361031</v>
+        <v>0.7942028985507247</v>
       </c>
     </row>
     <row r="23">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1424,16 +1424,16 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7988505747126436</v>
+        <v>0.8057142857142857</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7942857142857143</v>
+        <v>0.8057142857142857</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7965616045845271</v>
+        <v>0.8057142857142857</v>
       </c>
     </row>
     <row r="24">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1468,16 +1468,16 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8072289156626506</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7885714285714286</v>
+        <v>0.7657142857142857</v>
       </c>
       <c r="J24" t="n">
-        <v>0.80466472303207</v>
+        <v>0.785923753665689</v>
       </c>
     </row>
     <row r="25">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1512,16 +1512,16 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>246773155</v>
+        <v>50995999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.8218390804597702</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7885714285714286</v>
+        <v>0.8171428571428572</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7931034482758622</v>
+        <v>0.8194842406876791</v>
       </c>
     </row>
     <row r="26">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1552,20 +1552,20 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>14298463</v>
+        <v>246773155</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="I26" t="n">
         <v>0.8228571428571428</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8205128205128206</v>
+        <v>0.8275862068965516</v>
       </c>
     </row>
     <row r="27">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8103448275862069</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8080229226361031</v>
+        <v>0.8115942028985507</v>
       </c>
     </row>
     <row r="28">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1630,30 +1630,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7988505747126436</v>
+        <v>0.8284023668639053</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7942857142857143</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7965616045845271</v>
+        <v>0.813953488372093</v>
       </c>
     </row>
     <row r="29">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1674,30 +1674,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8165680473372781</v>
       </c>
       <c r="I29" t="n">
         <v>0.7885714285714286</v>
       </c>
       <c r="J29" t="n">
-        <v>0.80466472303207</v>
+        <v>0.8023255813953489</v>
       </c>
     </row>
     <row r="30">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1718,30 +1718,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>246773155</v>
+        <v>50995999</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.8187134502923976</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7885714285714286</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7931034482758622</v>
+        <v>0.8092485549132947</v>
       </c>
     </row>
     <row r="31">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>14298463</v>
+        <v>246773155</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8630952380952381</v>
+        <v>0.8430232558139535</v>
       </c>
       <c r="I31" t="n">
         <v>0.8285714285714286</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8454810495626822</v>
+        <v>0.8357348703170029</v>
       </c>
     </row>
     <row r="32">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1820,16 +1820,16 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8720930232558139</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8645533141210374</v>
+        <v>0.7871720116618075</v>
       </c>
     </row>
     <row r="33">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1864,16 +1864,16 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7885714285714286</v>
+        <v>0.8114285714285714</v>
       </c>
       <c r="J33" t="n">
-        <v>0.80466472303207</v>
+        <v>0.8160919540229885</v>
       </c>
     </row>
     <row r="34">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8392857142857143</v>
+        <v>0.8070175438596491</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.7885714285714286</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8221574344023325</v>
+        <v>0.7976878612716762</v>
       </c>
     </row>
     <row r="35">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1952,16 +1952,16 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>246773155</v>
+        <v>50995999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8238636363636364</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8262108262108263</v>
+        <v>0.8069164265129684</v>
       </c>
     </row>
     <row r="36">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1987,25 +1987,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>14298463</v>
+        <v>246773155</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8630952380952381</v>
+        <v>0.8245614035087719</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.8057142857142857</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8454810495626822</v>
+        <v>0.8150289017341041</v>
       </c>
     </row>
     <row r="37">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2036,20 +2036,20 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8720930232558139</v>
+        <v>0.8165680473372781</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7885714285714286</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8645533141210374</v>
+        <v>0.8023255813953489</v>
       </c>
     </row>
     <row r="38">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2080,20 +2080,20 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7885714285714286</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="J38" t="n">
-        <v>0.80466472303207</v>
+        <v>0.8228571428571428</v>
       </c>
     </row>
     <row r="39">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2124,20 +2124,20 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8392857142857143</v>
+        <v>0.7976878612716763</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.7885714285714286</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8221574344023325</v>
+        <v>0.7931034482758622</v>
       </c>
     </row>
     <row r="40">
@@ -2148,40 +2148,1844 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.8622754491017964</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.8421052631578948</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.8057142857142857</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8057142857142857</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.8057142857142857</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>t5-base</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7764705882352941</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.7630057803468209</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.7660818713450293</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7705882352941177</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.7683284457478007</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.8376623376623377</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.7588235294117647</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.7962962962962963</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.7869822485207101</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.7823529411764706</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.7846607669616519</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.7687861271676301</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.7823529411764706</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.7755102040816327</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.764367816091954</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.7823529411764706</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.7732558139534885</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.7341040462427746</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.7470588235294118</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.740524781341108</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.7674418604651163</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.7764705882352941</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.7719298245614037</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.803680981595092</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.7705882352941177</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.7867867867867867</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.7884057971014493</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.788235294117647</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.788235294117647</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.788235294117647</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.7869822485207101</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.7823529411764706</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.7846607669616519</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.7784431137724551</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.7715133531157269</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.8192771084337349</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.7823529411764706</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.7823529411764706</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.7823529411764706</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.7660818713450293</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.7705882352941177</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.7683284457478007</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.8047337278106509</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.8023598820058997</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.788235294117647</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.788235294117647</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.788235294117647</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.7758620689655172</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.7941176470588235</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.7848837209302325</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.783625730994152</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.788235294117647</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.7859237536656891</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>paraphrase</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.8128654970760234</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.7942857142857143</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.8034682080924856</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.8252148997134671</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.8208092485549133</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.8160919540229885</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.8497109826589595</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.8448275862068966</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
         <v>246773155</v>
       </c>
-      <c r="H40" t="n">
-        <v>0.8238636363636364</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="H66" t="n">
+        <v>0.8323699421965318</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.8275862068965516</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.813953488372093</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.8069164265129684</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.8045977011494253</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.8022922636103154</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H69" t="n">
         <v>0.8285714285714286</v>
       </c>
-      <c r="J40" t="n">
-        <v>0.8262108262108263</v>
+      <c r="I69" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.8497109826589595</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.8448275862068966</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.8248587570621468</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.8342857142857143</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.8295454545454545</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.8402366863905325</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.8255813953488372</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.8343558282208589</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.8047337278106508</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.8115942028985507</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.7885714285714286</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.80466472303207</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.8323699421965318</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.8275862068965516</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.844311377245509</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.8057142857142857</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.8245614035087719</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.8353658536585366</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.7828571428571428</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.8082595870206488</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.8313953488372093</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.8171428571428572</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.824207492795389</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.829971181556196</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/recap/at-PRF.xlsx
+++ b/analysis/recap/at-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,17 +454,47 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>micro_precision</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>micro_recall</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>micro_f1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>macro_precision</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>macro_recall</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>weighted_precision</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>weighted_recall</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>weighted_f1</t>
         </is>
       </c>
     </row>
@@ -503,13 +533,31 @@
         <v>14298463</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8343558282208589</v>
+        <v>0.8588957055214724</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8168168168168169</v>
+        <v>0.8408408408408408</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.8691460055096419</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.849862258953168</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.8526170798898072</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.8647058823529412</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.8352941176470586</v>
       </c>
     </row>
     <row r="3">
@@ -547,13 +595,31 @@
         <v>30288239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.8411764705882353</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.8411764705882353</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.8411764705882353</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.8581267217630855</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.8537190082644629</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8509803921568628</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.8411764705882353</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8380392156862744</v>
       </c>
     </row>
     <row r="4">
@@ -591,13 +657,31 @@
         <v>42511865</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.837465564738292</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8402203856749312</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.831404958677686</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.8392156862745099</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.8227450980392156</v>
       </c>
     </row>
     <row r="5">
@@ -635,13 +719,31 @@
         <v>50995999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8192771084337349</v>
+        <v>0.8493975903614458</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8</v>
+        <v>0.8294117647058824</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.8392857142857144</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.8581267217630855</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.8457300275482094</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8454545454545456</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8598039215686276</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.8294117647058824</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.8350980392156859</v>
       </c>
     </row>
     <row r="6">
@@ -679,13 +781,31 @@
         <v>246773155</v>
       </c>
       <c r="H6" t="n">
-        <v>0.791907514450867</v>
+        <v>0.8497109826589595</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8058823529411765</v>
+        <v>0.8647058823529412</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7988338192419824</v>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.8677685950413225</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8774104683195593</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.8652892561983472</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.8656862745098042</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.8647058823529412</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.8564705882352939</v>
       </c>
     </row>
     <row r="7">
@@ -723,13 +843,31 @@
         <v>14298463</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8414634146341463</v>
+        <v>0.8658536585365854</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8117647058823529</v>
+        <v>0.8352941176470589</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8263473053892215</v>
+        <v>0.8502994011976048</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.8705234159779615</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.849862258953168</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.8523415977961433</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8784313725490197</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.8352941176470589</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.8466666666666666</v>
       </c>
     </row>
     <row r="8">
@@ -767,13 +905,31 @@
         <v>30288239</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7797619047619048</v>
+        <v>0.8511904761904762</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7705882352941177</v>
+        <v>0.8411764705882353</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7751479289940829</v>
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.8457300275482095</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8360881542699726</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.8358126721763085</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8686274509803923</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.8411764705882353</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.8478431372549019</v>
       </c>
     </row>
     <row r="9">
@@ -811,13 +967,31 @@
         <v>42511865</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8319559228650139</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.8258953168044078</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8421568627450982</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.824705882352941</v>
       </c>
     </row>
     <row r="10">
@@ -855,13 +1029,31 @@
         <v>50995999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.8511904761904762</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7823529411764706</v>
+        <v>0.8411764705882353</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7869822485207101</v>
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8595041322314051</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8498622589531681</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.8498622589531681</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.8637254901960785</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.8411764705882353</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.8462745098039213</v>
       </c>
     </row>
     <row r="11">
@@ -899,13 +1091,31 @@
         <v>246773155</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.8160919540229885</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8117647058823529</v>
+        <v>0.8352941176470589</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8023255813953488</v>
+        <v>0.8255813953488372</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8388429752066118</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.8457300275482094</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.8352617079889807</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.8401960784313728</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.8352941176470589</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.8294117647058821</v>
       </c>
     </row>
     <row r="12">
@@ -943,13 +1153,31 @@
         <v>14298463</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8121212121212121</v>
+        <v>0.8363636363636363</v>
       </c>
       <c r="I12" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8117647058823529</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8</v>
+        <v>0.8238805970149253</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8360881542699725</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.8292011019283746</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.8269972451790634</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.8343137254901961</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.8117647058823529</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.816078431372549</v>
       </c>
     </row>
     <row r="13">
@@ -987,13 +1215,31 @@
         <v>30288239</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7456647398843931</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7588235294117647</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7521865889212828</v>
+        <v>0.8163265306122449</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.8402203856749312</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.8292011019283746</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.8323529411764706</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.8192156862745097</v>
       </c>
     </row>
     <row r="14">
@@ -1031,13 +1277,31 @@
         <v>42511865</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7674418604651163</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7719298245614037</v>
+        <v>0.8187134502923977</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8236914600550964</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.8305785123966942</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.8201101928374656</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.8284313725490199</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.8176470588235293</v>
       </c>
     </row>
     <row r="15">
@@ -1075,13 +1339,31 @@
         <v>50995999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8484848484848485</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8059701492537314</v>
+        <v>0.8358208955223881</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.8553719008264463</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.8443526170798897</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.841046831955923</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.8598039215686276</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.8296078431372548</v>
       </c>
     </row>
     <row r="16">
@@ -1119,13 +1401,31 @@
         <v>246773155</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8143712574850299</v>
+        <v>0.844311377245509</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>0.8294117647058824</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8071216617210683</v>
+        <v>0.8367952522255192</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.8498622589531681</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.8471074380165289</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.8413223140495869</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8480392156862745</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.8294117647058824</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.8301960784313723</v>
       </c>
     </row>
     <row r="17">
@@ -1163,13 +1463,31 @@
         <v>14298463</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8</v>
+        <v>0.8294117647058824</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>0.8294117647058824</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.8294117647058825</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.8319559228650139</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8360881542699724</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.8258953168044079</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8431372549019608</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.8294117647058824</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.8274509803921568</v>
       </c>
     </row>
     <row r="18">
@@ -1207,13 +1525,31 @@
         <v>30288239</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7456647398843931</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7588235294117647</v>
+        <v>0.8411764705882353</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7521865889212828</v>
+        <v>0.8338192419825073</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.831955922865014</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.8388429752066116</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.8283746556473829</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.8460784313725491</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.8411764705882353</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.8352941176470585</v>
       </c>
     </row>
     <row r="19">
@@ -1251,13 +1587,31 @@
         <v>42511865</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7810650887573964</v>
+        <v>0.834319526627219</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.8294117647058824</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7787610619469028</v>
+        <v>0.831858407079646</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8305785123966942</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8261707988980718</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.8450980392156864</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.8294117647058824</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.8301960784313723</v>
       </c>
     </row>
     <row r="20">
@@ -1295,13 +1649,31 @@
         <v>50995999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7823529411764706</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7869822485207101</v>
+        <v>0.8284023668639053</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.8305785123966942</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.8292011019283746</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.8217630853994491</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.8450980392156864</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.8247058823529411</v>
       </c>
     </row>
     <row r="21">
@@ -1339,13 +1711,31 @@
         <v>246773155</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7869822485207101</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7823529411764706</v>
+        <v>0.8411764705882353</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7846607669616519</v>
+        <v>0.8436578171091446</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.847107438016529</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.8471074380165289</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.8396694214876034</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.8558823529411764</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8411764705882353</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.8396078431372547</v>
       </c>
     </row>
     <row r="22">
@@ -1383,13 +1773,31 @@
         <v>14298463</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8058823529411765</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7828571428571428</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7942028985507247</v>
+        <v>0.8115942028985507</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.8243801652892563</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.8126721763085401</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.8098386462022826</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.8347619047619048</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.8057414965986394</v>
       </c>
     </row>
     <row r="23">
@@ -1427,13 +1835,31 @@
         <v>30288239</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.8285123966942148</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.8278236914600553</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.8203069657615112</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.8404761904761904</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.8226938775510203</v>
       </c>
     </row>
     <row r="24">
@@ -1471,13 +1897,31 @@
         <v>42511865</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8072289156626506</v>
+        <v>0.8313253012048193</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7657142857142857</v>
+        <v>0.7885714285714286</v>
       </c>
       <c r="J24" t="n">
-        <v>0.785923753665689</v>
+        <v>0.8093841642228738</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.8209366391184574</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.8002754820936641</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.8027548209366391</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.8390476190476192</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.7885714285714286</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.8024761904761905</v>
       </c>
     </row>
     <row r="25">
@@ -1515,13 +1959,31 @@
         <v>50995999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8218390804597702</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8171428571428572</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8194842406876791</v>
+        <v>0.8252148997134671</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.8450413223140497</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.8429752066115703</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.8384887839433295</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.8347619047619048</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.822312925170068</v>
       </c>
     </row>
     <row r="26">
@@ -1559,13 +2021,31 @@
         <v>246773155</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8323699421965318</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8228571428571428</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8275862068965516</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.8347107438016529</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.8258953168044078</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.8504761904761905</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.8295238095238094</v>
       </c>
     </row>
     <row r="27">
@@ -1603,13 +2083,31 @@
         <v>14298463</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8411764705882353</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.8171428571428572</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8115942028985507</v>
+        <v>0.8289855072463768</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.8312672176308541</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.8195592286501377</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.8167256985438804</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.8519047619047619</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.8171428571428572</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.8228843537414965</v>
       </c>
     </row>
     <row r="28">
@@ -1647,13 +2145,31 @@
         <v>30288239</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8284023668639053</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>0.8171428571428572</v>
       </c>
       <c r="J28" t="n">
-        <v>0.813953488372093</v>
+        <v>0.8313953488372092</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.8353994490358128</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.8264462809917358</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.8236127508854781</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.8490476190476191</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.8171428571428572</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.8238367346938776</v>
       </c>
     </row>
     <row r="29">
@@ -1691,13 +2207,31 @@
         <v>42511865</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8165680473372781</v>
+        <v>0.8402366863905325</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7885714285714286</v>
+        <v>0.8114285714285714</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8023255813953489</v>
+        <v>0.8255813953488372</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.8360881542699725</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.8154269972451792</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.8179063360881543</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.861904761904762</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.8253333333333334</v>
       </c>
     </row>
     <row r="30">
@@ -1735,13 +2269,31 @@
         <v>50995999</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8187134502923976</v>
+        <v>0.8362573099415205</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.8171428571428572</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8092485549132947</v>
+        <v>0.8265895953757226</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.8319559228650139</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.8140495867768596</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.8173553719008264</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.8561904761904763</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.8171428571428572</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.8289523809523808</v>
       </c>
     </row>
     <row r="31">
@@ -1779,13 +2331,31 @@
         <v>246773155</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8430232558139535</v>
+        <v>0.8546511627906976</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.84</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8357348703170029</v>
+        <v>0.8472622478386167</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.8443526170798898</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.8374655647382919</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.8676190476190476</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.8439999999999998</v>
       </c>
     </row>
     <row r="32">
@@ -1823,13 +2393,31 @@
         <v>14298463</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7871720116618075</v>
+        <v>0.7930029154518949</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.8154269972451791</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.8044077134986227</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.8011019283746557</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.7771428571428571</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.7828571428571428</v>
       </c>
     </row>
     <row r="33">
@@ -1867,13 +2455,31 @@
         <v>30288239</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8208092485549133</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8114285714285714</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8160919540229885</v>
+        <v>0.8275862068965516</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.8312672176308541</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.8305785123966943</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.8233372687918143</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.8433333333333334</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.8242176870748299</v>
       </c>
     </row>
     <row r="34">
@@ -1911,13 +2517,31 @@
         <v>42511865</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8070175438596491</v>
+        <v>0.8304093567251462</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7885714285714286</v>
+        <v>0.8114285714285714</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7976878612716762</v>
+        <v>0.8208092485549132</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.8230027548209368</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.8181818181818185</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.8139708776072412</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.8376190476190477</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.8162176870748299</v>
       </c>
     </row>
     <row r="35">
@@ -1955,13 +2579,31 @@
         <v>50995999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.813953488372093</v>
+        <v>0.8313953488372093</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.8171428571428572</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8069164265129684</v>
+        <v>0.824207492795389</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.8286501377410468</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.8264462809917357</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.821900826446281</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.8321904761904761</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.8171428571428572</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.8174285714285715</v>
       </c>
     </row>
     <row r="36">
@@ -1999,13 +2641,31 @@
         <v>246773155</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8245614035087719</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8150289017341041</v>
+        <v>0.8323699421965317</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.8381542699724518</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.8347107438016529</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.8277449822904368</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.8490476190476191</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.8247891156462585</v>
       </c>
     </row>
     <row r="37">
@@ -2043,13 +2703,31 @@
         <v>14298463</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8165680473372781</v>
+        <v>0.834319526627219</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7885714285714286</v>
+        <v>0.8057142857142857</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8023255813953489</v>
+        <v>0.8197674418604651</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.8319559228650139</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.8236914600550965</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.8170798898071626</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.8495238095238097</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.8057142857142857</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.8140952380952383</v>
       </c>
     </row>
     <row r="38">
@@ -2087,13 +2765,31 @@
         <v>30288239</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8228571428571428</v>
+        <v>0.84</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8228571428571428</v>
+        <v>0.84</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8228571428571428</v>
+        <v>0.8399999999999999</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.8436639118457301</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.8374655647382923</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.833530106257379</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.8661904761904763</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.8444081632653061</v>
       </c>
     </row>
     <row r="39">
@@ -2131,13 +2827,31 @@
         <v>42511865</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7885714285714286</v>
+        <v>0.8057142857142857</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7931034482758622</v>
+        <v>0.8103448275862069</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.8147382920110192</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.8057851239669422</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.8032270759543487</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.8366666666666666</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.8057142857142857</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.8124081632653062</v>
       </c>
     </row>
     <row r="40">
@@ -2175,13 +2889,31 @@
         <v>50995999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8622754491017964</v>
+        <v>0.874251497005988</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8228571428571428</v>
+        <v>0.8342857142857143</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8421052631578948</v>
+        <v>0.8538011695906432</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.8650137741046833</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.8443526170798898</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.8479338842975206</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.8790476190476191</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.8342857142857143</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.8466666666666665</v>
       </c>
     </row>
     <row r="41">
@@ -2219,13 +2951,31 @@
         <v>246773155</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.8285714285714286</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.8243801652892562</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.8347107438016529</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.8181031090122</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.8452380952380953</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.8238367346938776</v>
       </c>
     </row>
     <row r="42">
@@ -2263,13 +3013,31 @@
         <v>14298463</v>
       </c>
       <c r="H42" t="n">
-        <v>0.75</v>
+        <v>0.8068181818181818</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.8352941176470589</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7630057803468209</v>
+        <v>0.8208092485549133</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.8333333333333335</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.8498622589531681</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.8327823691460055</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.8333333333333335</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.8352941176470589</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.8243137254901959</v>
       </c>
     </row>
     <row r="43">
@@ -2307,13 +3075,31 @@
         <v>30288239</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7660818713450293</v>
+        <v>0.8187134502923976</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7705882352941177</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7683284457478007</v>
+        <v>0.8211143695014662</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.8292011019283746</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.8319559228650139</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.8253443526170799</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.8333333333333335</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.8227450980392157</v>
       </c>
     </row>
     <row r="44">
@@ -2351,13 +3137,31 @@
         <v>42511865</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8376623376623377</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7588235294117647</v>
+        <v>0.7823529411764706</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7962962962962963</v>
+        <v>0.8209876543209876</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.8512396694214877</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.8099173553719008</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.8236914600550964</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.7823529411764706</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.8049019607843136</v>
       </c>
     </row>
     <row r="45">
@@ -2395,13 +3199,31 @@
         <v>50995999</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7869822485207101</v>
+        <v>0.8284023668639053</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7823529411764706</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7846607669616519</v>
+        <v>0.8259587020648966</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.834710743801653</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.8319559228650139</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.8289256198347108</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.8362745098039217</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.8243137254901957</v>
       </c>
     </row>
     <row r="46">
@@ -2439,13 +3261,31 @@
         <v>246773155</v>
       </c>
       <c r="H46" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7823529411764706</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7755102040816327</v>
+        <v>0.8163265306122449</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.825068870523416</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.8360881542699725</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.8231404958677687</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.8303921568627453</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.8188235294117646</v>
       </c>
     </row>
     <row r="47">
@@ -2483,13 +3323,31 @@
         <v>14298463</v>
       </c>
       <c r="H47" t="n">
-        <v>0.764367816091954</v>
+        <v>0.8160919540229885</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7823529411764706</v>
+        <v>0.8352941176470589</v>
       </c>
       <c r="J47" t="n">
-        <v>0.7732558139534885</v>
+        <v>0.8255813953488372</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.8168044077134988</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.825068870523416</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.8140495867768596</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.8372549019607843</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.8352941176470589</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.8282352941176467</v>
       </c>
     </row>
     <row r="48">
@@ -2527,13 +3385,31 @@
         <v>30288239</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7341040462427746</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7470588235294118</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J48" t="n">
-        <v>0.740524781341108</v>
+        <v>0.8163265306122449</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.8154269972451791</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.8154269972451791</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.8107438016528925</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.8343137254901961</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.8235294117647057</v>
       </c>
     </row>
     <row r="49">
@@ -2571,13 +3447,31 @@
         <v>42511865</v>
       </c>
       <c r="H49" t="n">
-        <v>0.7674418604651163</v>
+        <v>0.8197674418604651</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7764705882352941</v>
+        <v>0.8294117647058824</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7719298245614037</v>
+        <v>0.8245614035087719</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.8271349862258955</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.8264462809917357</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.8227863046044864</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.8338235294117649</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.8294117647058824</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.8261064425770306</v>
       </c>
     </row>
     <row r="50">
@@ -2615,13 +3509,31 @@
         <v>50995999</v>
       </c>
       <c r="H50" t="n">
-        <v>0.803680981595092</v>
+        <v>0.8404907975460123</v>
       </c>
       <c r="I50" t="n">
-        <v>0.7705882352941177</v>
+        <v>0.8058823529411765</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7867867867867867</v>
+        <v>0.8228228228228228</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.834710743801653</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.8099173553719008</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.8165289256198348</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.8490196078431373</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.8058823529411765</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.8192156862745097</v>
       </c>
     </row>
     <row r="51">
@@ -2659,13 +3571,31 @@
         <v>246773155</v>
       </c>
       <c r="H51" t="n">
-        <v>0.7771428571428571</v>
+        <v>0.8057142857142857</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.8294117647058824</v>
       </c>
       <c r="J51" t="n">
-        <v>0.7884057971014493</v>
+        <v>0.8173913043478261</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.8209366391184574</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.8278236914600552</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.8176308539944905</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.8392156862745099</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.8294117647058824</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.8266666666666664</v>
       </c>
     </row>
     <row r="52">
@@ -2703,13 +3633,31 @@
         <v>14298463</v>
       </c>
       <c r="H52" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8176470588235294</v>
       </c>
       <c r="I52" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8176470588235294</v>
       </c>
       <c r="J52" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8176470588235294</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.8278236914600552</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.8236914600550965</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.8192837465564737</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.8382352941176472</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.8176470588235294</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.8196078431372547</v>
       </c>
     </row>
     <row r="53">
@@ -2747,13 +3695,31 @@
         <v>30288239</v>
       </c>
       <c r="H53" t="n">
-        <v>0.7869822485207101</v>
+        <v>0.834319526627219</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7823529411764706</v>
+        <v>0.8294117647058824</v>
       </c>
       <c r="J53" t="n">
-        <v>0.7846607669616519</v>
+        <v>0.831858407079646</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.8484848484848486</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.8415977961432508</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.8399449035812672</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.8460784313725491</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.8294117647058824</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.8305882352941174</v>
       </c>
     </row>
     <row r="54">
@@ -2791,13 +3757,31 @@
         <v>42511865</v>
       </c>
       <c r="H54" t="n">
-        <v>0.7784431137724551</v>
+        <v>0.8323353293413174</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.8176470588235294</v>
       </c>
       <c r="J54" t="n">
-        <v>0.7715133531157269</v>
+        <v>0.8249258160237388</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.84435261707989</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.831129476584022</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.8460784313725492</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.8176470588235294</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.8205882352941173</v>
       </c>
     </row>
     <row r="55">
@@ -2835,13 +3819,31 @@
         <v>50995999</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8192771084337349</v>
+        <v>0.8554216867469879</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>0.8352941176470589</v>
       </c>
       <c r="J55" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.8452380952380952</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.837465564738292</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.8380165289256198</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.8607843137254902</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.8352941176470589</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.8415686274509802</v>
       </c>
     </row>
     <row r="56">
@@ -2879,13 +3881,31 @@
         <v>246773155</v>
       </c>
       <c r="H56" t="n">
-        <v>0.7823529411764706</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="I56" t="n">
-        <v>0.7823529411764706</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J56" t="n">
-        <v>0.7823529411764706</v>
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.8374655647382923</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.8319559228650139</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.8292011019283746</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.8411764705882354</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.825098039215686</v>
       </c>
     </row>
     <row r="57">
@@ -2923,13 +3943,31 @@
         <v>14298463</v>
       </c>
       <c r="H57" t="n">
-        <v>0.7660818713450293</v>
+        <v>0.8187134502923976</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7705882352941177</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J57" t="n">
-        <v>0.7683284457478007</v>
+        <v>0.8211143695014662</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.8140495867768596</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.8071625344352616</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.8343137254901963</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.8184313725490194</v>
       </c>
     </row>
     <row r="58">
@@ -2967,13 +4005,31 @@
         <v>30288239</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8047337278106509</v>
+        <v>0.8579881656804734</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="J58" t="n">
-        <v>0.8023598820058997</v>
+        <v>0.8554572271386431</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.8498622589531682</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.8457300275482095</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.8424242424242423</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.8656862745098042</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.8517647058823526</v>
       </c>
     </row>
     <row r="59">
@@ -3011,13 +4067,31 @@
         <v>42511865</v>
       </c>
       <c r="H59" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="I59" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J59" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.8292011019283747</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.8236914600550964</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.8201101928374654</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.8401960784313728</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.8235294117647055</v>
       </c>
     </row>
     <row r="60">
@@ -3055,13 +4129,31 @@
         <v>50995999</v>
       </c>
       <c r="H60" t="n">
-        <v>0.7758620689655172</v>
+        <v>0.8160919540229885</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.8352941176470589</v>
       </c>
       <c r="J60" t="n">
-        <v>0.7848837209302325</v>
+        <v>0.8255813953488372</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.8209366391184575</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.8305785123966943</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.8198347107438017</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.835294117647059</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.8352941176470589</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.828627450980392</v>
       </c>
     </row>
     <row r="61">
@@ -3099,13 +4191,31 @@
         <v>246773155</v>
       </c>
       <c r="H61" t="n">
-        <v>0.783625730994152</v>
+        <v>0.8128654970760234</v>
       </c>
       <c r="I61" t="n">
-        <v>0.788235294117647</v>
+        <v>0.8176470588235294</v>
       </c>
       <c r="J61" t="n">
-        <v>0.7859237536656891</v>
+        <v>0.8152492668621701</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.8126721763085399</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.8140495867768596</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.8077134986225896</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.8313725490196079</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.8176470588235294</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.8180392156862745</v>
       </c>
     </row>
     <row r="62">
@@ -3143,13 +4253,31 @@
         <v>14298463</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8128654970760234</v>
+        <v>0.8245614035087719</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7942857142857143</v>
+        <v>0.8057142857142857</v>
       </c>
       <c r="J62" t="n">
-        <v>0.8034682080924856</v>
+        <v>0.8150289017341041</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.837465564738292</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.8319559228650137</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.8247933884297521</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.838095238095238</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.8057142857142857</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.8083809523809524</v>
       </c>
     </row>
     <row r="63">
@@ -3187,13 +4315,31 @@
         <v>30288239</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8228571428571428</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="J63" t="n">
-        <v>0.8252148997134671</v>
+        <v>0.8309455587392551</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.8402203856749312</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.837465564738292</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.8325068870523417</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.8476190476190477</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.8308571428571428</v>
       </c>
     </row>
     <row r="64">
@@ -3231,13 +4377,31 @@
         <v>42511865</v>
       </c>
       <c r="H64" t="n">
-        <v>0.8208092485549133</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8114285714285714</v>
+        <v>0.8171428571428572</v>
       </c>
       <c r="J64" t="n">
-        <v>0.8160919540229885</v>
+        <v>0.8218390804597702</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.8305785123966942</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.825068870523416</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.8203856749311295</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.8419047619047618</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.8171428571428572</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.8199999999999998</v>
       </c>
     </row>
     <row r="65">
@@ -3275,13 +4439,31 @@
         <v>50995999</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8497109826589595</v>
+        <v>0.8554913294797688</v>
       </c>
       <c r="I65" t="n">
-        <v>0.84</v>
+        <v>0.8457142857142858</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8448275862068966</v>
+        <v>0.8505747126436781</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.8546831955922866</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.847107438016529</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.8453758362849273</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.8671428571428571</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.8457142857142858</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.8497414965986395</v>
       </c>
     </row>
     <row r="66">
@@ -3319,13 +4501,31 @@
         <v>246773155</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8323699421965318</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8228571428571428</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="J66" t="n">
-        <v>0.8275862068965516</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.8491735537190083</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.8443526170798898</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.8415190869736323</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.8442857142857143</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.8303129251700678</v>
       </c>
     </row>
     <row r="67">
@@ -3363,13 +4563,31 @@
         <v>14298463</v>
       </c>
       <c r="H67" t="n">
-        <v>0.813953488372093</v>
+        <v>0.8255813953488372</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>0.8114285714285714</v>
       </c>
       <c r="J67" t="n">
-        <v>0.8069164265129684</v>
+        <v>0.8184438040345821</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.8147382920110193</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.8071625344352619</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.8048799685163321</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.8347619047619048</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.815455782312925</v>
       </c>
     </row>
     <row r="68">
@@ -3407,13 +4625,31 @@
         <v>30288239</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8045977011494253</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8022922636103154</v>
+        <v>0.8252148997134671</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.8202479338842975</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.8195592286501377</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.8134199134199134</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.8376190476190475</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.8226938775510203</v>
       </c>
     </row>
     <row r="69">
@@ -3451,13 +4687,31 @@
         <v>42511865</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.8342857142857143</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.8342857142857143</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8285714285714286</v>
+        <v>0.8342857142857143</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.8271349862258954</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.8264462809917357</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.8203069657615113</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.8490476190476189</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.8342857142857143</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.8341224489795918</v>
       </c>
     </row>
     <row r="70">
@@ -3495,13 +4749,31 @@
         <v>50995999</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8497109826589595</v>
+        <v>0.8554913294797688</v>
       </c>
       <c r="I70" t="n">
-        <v>0.84</v>
+        <v>0.8457142857142858</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8448275862068966</v>
+        <v>0.8505747126436781</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.8505509641873279</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.8429752066115703</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.8412436048799686</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.8671428571428571</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.8457142857142858</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.8497414965986395</v>
       </c>
     </row>
     <row r="71">
@@ -3547,6 +4819,24 @@
       <c r="J71" t="n">
         <v>0.8571428571428571</v>
       </c>
+      <c r="K71" t="n">
+        <v>0.8588154269972452</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.8539944903581268</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.8511609602518694</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.8728571428571429</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.8588843537414966</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3583,13 +4873,31 @@
         <v>14298463</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8248587570621468</v>
+        <v>0.8305084745762712</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8342857142857143</v>
+        <v>0.84</v>
       </c>
       <c r="J72" t="n">
-        <v>0.8295454545454545</v>
+        <v>0.8352272727272728</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.8285123966942149</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.8388429752066117</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.8288469106650924</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.8376190476190477</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.8337414965986394</v>
       </c>
     </row>
     <row r="73">
@@ -3627,13 +4935,31 @@
         <v>30288239</v>
       </c>
       <c r="H73" t="n">
-        <v>0.8402366863905325</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8114285714285714</v>
+        <v>0.8171428571428572</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8255813953488372</v>
+        <v>0.8313953488372092</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.8402203856749312</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.8278236914600553</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.8275482093663913</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.8485714285714285</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.8171428571428572</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.8241904761904761</v>
       </c>
     </row>
     <row r="74">
@@ -3671,13 +4997,31 @@
         <v>42511865</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8343558282208589</v>
+        <v>0.8404907975460123</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7771428571428571</v>
+        <v>0.7828571428571428</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8047337278106508</v>
+        <v>0.8106508875739644</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.8429752066115702</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.8168044077134987</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.8242424242424242</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.8314285714285714</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.7828571428571428</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.7982857142857143</v>
       </c>
     </row>
     <row r="75">
@@ -3715,13 +5059,31 @@
         <v>50995999</v>
       </c>
       <c r="H75" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8294117647058824</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>0.8057142857142857</v>
       </c>
       <c r="J75" t="n">
-        <v>0.8115942028985507</v>
+        <v>0.8173913043478261</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8190082644628098</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.8428571428571429</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.8057142857142857</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.815047619047619</v>
       </c>
     </row>
     <row r="76">
@@ -3759,13 +5121,31 @@
         <v>246773155</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7885714285714286</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
-        <v>0.80466472303207</v>
+        <v>0.816326530612245</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.8347107438016529</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.8223140495867769</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.822314049586777</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.8342857142857143</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.8085714285714284</v>
       </c>
     </row>
     <row r="77">
@@ -3803,13 +5183,31 @@
         <v>14298463</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8323699421965318</v>
+        <v>0.8439306358381503</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8228571428571428</v>
+        <v>0.8342857142857143</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8275862068965516</v>
+        <v>0.839080459770115</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.8298898071625345</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.8236914600550965</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.8216843762298308</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.8557142857142858</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.8342857142857143</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.8386938775510202</v>
       </c>
     </row>
     <row r="78">
@@ -3847,13 +5245,31 @@
         <v>30288239</v>
       </c>
       <c r="H78" t="n">
-        <v>0.844311377245509</v>
+        <v>0.8622754491017964</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8057142857142857</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8245614035087719</v>
+        <v>0.8421052631578948</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.8429752066115702</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.8140495867768596</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.8214876033057851</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.8392380952380952</v>
       </c>
     </row>
     <row r="79">
@@ -3891,13 +5307,31 @@
         <v>42511865</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8353658536585366</v>
+        <v>0.8658536585365854</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7828571428571428</v>
+        <v>0.8114285714285714</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8082595870206488</v>
+        <v>0.8377581120943953</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.8526170798898072</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.8250688705234162</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.8338842975206612</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.8114285714285714</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.8297142857142856</v>
       </c>
     </row>
     <row r="80">
@@ -3935,13 +5369,31 @@
         <v>50995999</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8313953488372093</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8171428571428572</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="J80" t="n">
-        <v>0.824207492795389</v>
+        <v>0.829971181556196</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.8347107438016528</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.825068870523416</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.8245179063360881</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.8485714285714285</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.8228571428571428</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.8293333333333333</v>
       </c>
     </row>
     <row r="81">
@@ -3979,13 +5431,31 @@
         <v>246773155</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.8488372093023255</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8228571428571428</v>
+        <v>0.8342857142857143</v>
       </c>
       <c r="J81" t="n">
-        <v>0.829971181556196</v>
+        <v>0.8414985590778098</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.8402203856749312</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.8360881542699725</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.8316804407713501</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.8561904761904763</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.8342857142857143</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.8377142857142856</v>
       </c>
     </row>
   </sheetData>
